--- a/Output Data Tables/AFAT Outputs/Employee Tables/2017/Labor_Cost_per_Employee_by_Airline_2017.xlsx
+++ b/Output Data Tables/AFAT Outputs/Employee Tables/2017/Labor_Cost_per_Employee_by_Airline_2017.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="30">
   <si>
     <t>Row</t>
   </si>
@@ -87,10 +87,22 @@
     <t>SkyWest</t>
   </si>
   <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
+  </si>
+  <si>
     <t>All Airlines</t>
   </si>
   <si>
-    <t>Labor Costs per Employee</t>
+    <t>Labor Cost per Employee</t>
   </si>
 </sst>
 </file>
@@ -136,11 +148,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
-    <col min="2" max="2" width="23.85546875" customWidth="true"/>
+    <col min="2" max="2" width="23" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -148,7 +160,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -156,7 +168,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>106122</v>
+        <v>108783</v>
       </c>
     </row>
     <row r="3">
@@ -164,7 +176,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>97499</v>
+        <v>118258</v>
       </c>
     </row>
     <row r="4">
@@ -172,7 +184,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>84628</v>
+        <v>121662</v>
       </c>
     </row>
     <row r="5">
@@ -180,7 +192,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>130191</v>
+        <v>100338</v>
       </c>
     </row>
     <row r="6">
@@ -196,7 +208,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>127383</v>
+        <v>135543</v>
       </c>
     </row>
     <row r="8">
@@ -204,7 +216,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>105096</v>
+        <v>109492</v>
       </c>
     </row>
     <row r="9">
@@ -212,7 +224,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>95237</v>
+        <v>102996</v>
       </c>
     </row>
     <row r="10">
@@ -220,7 +232,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>112789</v>
+        <v>118112</v>
       </c>
     </row>
     <row r="11">
@@ -228,7 +240,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>141142</v>
+        <v>141195</v>
       </c>
     </row>
     <row r="12">
@@ -236,7 +248,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>78256</v>
+        <v>74319</v>
       </c>
     </row>
     <row r="13">
@@ -244,7 +256,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>77599</v>
+        <v>79079</v>
       </c>
     </row>
     <row r="14">
@@ -252,7 +264,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>118887</v>
+        <v>136565</v>
       </c>
     </row>
     <row r="15">
@@ -268,7 +280,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>87230</v>
+        <v>80308</v>
       </c>
     </row>
     <row r="17">
@@ -276,7 +288,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>48514</v>
+        <v>50353</v>
       </c>
     </row>
     <row r="18">
@@ -284,7 +296,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>59779</v>
+        <v>70463</v>
       </c>
     </row>
     <row r="19">
@@ -292,7 +304,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>63442</v>
+        <v>64674</v>
       </c>
     </row>
     <row r="20">
@@ -300,7 +312,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>41497</v>
+        <v>49219</v>
       </c>
     </row>
     <row r="21">
@@ -316,7 +328,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>59298</v>
+        <v>69291</v>
       </c>
     </row>
     <row r="23">
@@ -324,7 +336,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>90655</v>
+        <v>80954</v>
       </c>
     </row>
     <row r="24">
@@ -332,7 +344,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>75168</v>
+        <v>73379</v>
       </c>
     </row>
     <row r="25">
@@ -340,7 +352,39 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>107525</v>
+        <v>130652</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>129316</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>92543</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>65518</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>121814</v>
       </c>
     </row>
   </sheetData>
